--- a/density_guess.xlsx
+++ b/density_guess.xlsx
@@ -418,2243 +418,2243 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0.4149092960657101</v>
+        <v>1.05613992459839</v>
       </c>
       <c r="B1" t="n">
-        <v>-0.0262836238652753</v>
+        <v>-0.2880302128933709</v>
       </c>
       <c r="C1" t="n">
-        <v>0.2085031115321895</v>
+        <v>0.1071925414148716</v>
       </c>
       <c r="D1" t="n">
-        <v>-0.2236193831300372</v>
+        <v>-3.98916196046823e-16</v>
       </c>
       <c r="E1" t="n">
-        <v>-0.06202759438232119</v>
+        <v>3.897475924526549e-16</v>
       </c>
       <c r="F1" t="n">
-        <v>0.1631798271935227</v>
+        <v>0.008573524431539383</v>
       </c>
       <c r="G1" t="n">
-        <v>-0.01700340897766904</v>
+        <v>-1.544464937652877e-16</v>
       </c>
       <c r="H1" t="n">
-        <v>-0.01310934176527894</v>
+        <v>-2.464799458951021e-16</v>
       </c>
       <c r="I1" t="n">
-        <v>0.1161740999958441</v>
+        <v>0.01969563737657378</v>
       </c>
       <c r="J1" t="n">
-        <v>-0.2078067931183774</v>
+        <v>-4.41560759342019e-05</v>
       </c>
       <c r="K1" t="n">
-        <v>-0.1745743292832573</v>
+        <v>0.009909728117548075</v>
       </c>
       <c r="L1" t="n">
-        <v>0.1263089958957333</v>
+        <v>-0.03331951698960246</v>
       </c>
       <c r="M1" t="n">
-        <v>0.1285055644581466</v>
+        <v>3.386327417517696e-16</v>
       </c>
       <c r="N1" t="n">
-        <v>0.1173043569348611</v>
+        <v>6.31796188350958e-17</v>
       </c>
       <c r="O1" t="n">
-        <v>0.08134899582738155</v>
+        <v>-0.003875030025991172</v>
       </c>
       <c r="P1" t="n">
-        <v>-0.1205691247169175</v>
+        <v>1.444733700211302e-16</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.1672446946576478</v>
+        <v>-3.160818440098758e-16</v>
       </c>
       <c r="R1" t="n">
-        <v>-0.003426113867490373</v>
+        <v>0.003492041624121089</v>
       </c>
       <c r="S1" t="n">
-        <v>0.002887341203119973</v>
+        <v>0.002322234021151529</v>
       </c>
       <c r="T1" t="n">
-        <v>-0.1051860925764446</v>
+        <v>-0.01306275909120277</v>
       </c>
       <c r="U1" t="n">
-        <v>-0.1108421246107498</v>
+        <v>-0.02856029426917964</v>
       </c>
       <c r="V1" t="n">
-        <v>0.07460627977017599</v>
+        <v>9.867811080087707e-16</v>
       </c>
       <c r="W1" t="n">
-        <v>-0.001208669037817883</v>
+        <v>-8.177888879738922e-16</v>
       </c>
       <c r="X1" t="n">
-        <v>0.2055228808198214</v>
+        <v>-0.009214931426535856</v>
       </c>
       <c r="Y1" t="n">
-        <v>0.1005123871607017</v>
+        <v>-5.19644120032156e-16</v>
       </c>
       <c r="Z1" t="n">
-        <v>-0.02988812232989752</v>
+        <v>7.76283353904702e-16</v>
       </c>
       <c r="AA1" t="n">
-        <v>-0.04285544467147286</v>
+        <v>0.05859469609200812</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.0262836238652753</v>
+        <v>-0.2880302128933709</v>
       </c>
       <c r="B2" t="n">
-        <v>1.604839215582338</v>
+        <v>1.367857915220493</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.656063709853732</v>
+        <v>-0.3983966623683476</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1747184262437651</v>
+        <v>8.938637001676478e-15</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01779449026639651</v>
+        <v>-3.937870466132445e-15</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2135095479996891</v>
+        <v>-0.02956718859924126</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.305343134968752</v>
+        <v>-1.137962990505073e-16</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1527188379035007</v>
+        <v>1.70356258769867e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.200996398396036</v>
+        <v>-0.07078715831251735</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3134260700816869</v>
+        <v>0.009909728117547019</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2444302676276843</v>
+        <v>-0.08140288302674654</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.311735988600461</v>
+        <v>0.1280626426563356</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1665765601027066</v>
+        <v>-2.336738628937137e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1036776627857329</v>
+        <v>-1.346720420001046e-15</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2356088425466359</v>
+        <v>0.003585501122984139</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3157358118738263</v>
+        <v>-5.079632101687527e-16</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2313498355330804</v>
+        <v>1.68307476419551e-15</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4813350308291595</v>
+        <v>-0.007015030267726976</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01675257734977409</v>
+        <v>-0.01293754325852874</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3483231732877</v>
+        <v>0.06677051010835432</v>
       </c>
       <c r="U2" t="n">
-        <v>2.191099469329304</v>
+        <v>0.1006846726786921</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6003953609481625</v>
+        <v>-5.944950718855072e-15</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1132844784114047</v>
+        <v>4.6633436322233e-15</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03603792382736411</v>
+        <v>0.06678716967013644</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5773482100575251</v>
+        <v>2.740115225207197e-15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2840147940456794</v>
+        <v>-3.909294601961608e-15</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.915484044500383</v>
+        <v>-0.2242719444264757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2085031115321895</v>
+        <v>0.1071925414148716</v>
       </c>
       <c r="B3" t="n">
-        <v>-3.656063709853732</v>
+        <v>-0.3983966623683476</v>
       </c>
       <c r="C3" t="n">
-        <v>14.16640447144028</v>
+        <v>0.1814885846271273</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3866736406345646</v>
+        <v>1.758902893784434e-15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1900178179022771</v>
+        <v>-5.897148832472194e-15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6980412247350894</v>
+        <v>-0.1890775731357466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.213134475810546</v>
+        <v>-1.234117927627621e-17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2629337532790755</v>
+        <v>6.997825498185122e-16</v>
       </c>
       <c r="I3" t="n">
-        <v>4.495024505970179</v>
+        <v>0.08486288721808025</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3396723767934992</v>
+        <v>-0.03331951698959924</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3634671591147606</v>
+        <v>0.1280626426563304</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.184670637115342</v>
+        <v>-0.1038550674043969</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8040308144744107</v>
+        <v>-1.604400350251715e-14</v>
       </c>
       <c r="N3" t="n">
-        <v>1.065561755274843</v>
+        <v>2.584755919814277e-15</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2530626625369093</v>
+        <v>-0.0522177621502811</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9182837456742124</v>
+        <v>3.187534276902286e-15</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.368226769666174</v>
+        <v>-6.091245149046563e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0696969552455096</v>
+        <v>0.03702968471916351</v>
       </c>
       <c r="S3" t="n">
-        <v>1.047427326759348</v>
+        <v>0.008556621213709887</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6431942298007601</v>
+        <v>-0.04474285512117276</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.965370068784794</v>
+        <v>-0.03188771358238395</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26120655825385</v>
+        <v>-5.481556824273983e-16</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4647946639524154</v>
+        <v>-4.942166928248169e-16</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3269147352865343</v>
+        <v>0.09424145154437029</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.431276599340738</v>
+        <v>-1.665275719496698e-15</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8984252603624675</v>
+        <v>5.799998432542377e-16</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.05836529264401</v>
+        <v>0.09862789552489724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.2236193831300372</v>
+        <v>-3.98916196046823e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1747184262437651</v>
+        <v>8.938637001676478e-15</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3866736406345646</v>
+        <v>1.758902893784434e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.463886820513919</v>
+        <v>1.135528060123846</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0302587164462409</v>
+        <v>-1.526286676003655e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1189345233099394</v>
+        <v>2.153943972066077e-14</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1100849562828111</v>
+        <v>-0.2018195271737731</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04510959276708901</v>
+        <v>5.672469226565263e-16</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07905262123336666</v>
+        <v>-5.575630527048868e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03622607011510384</v>
+        <v>5.2262366862049e-16</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05082543940799338</v>
+        <v>5.450773356742642e-15</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1786470417678356</v>
+        <v>-3.816248099857366e-14</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2693792778506841</v>
+        <v>-0.005859552357678273</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06524060910164985</v>
+        <v>-2.067450063437449e-16</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03174796937395418</v>
+        <v>1.350674140835183e-14</v>
       </c>
       <c r="P4" t="n">
-        <v>0.054352283599816</v>
+        <v>-0.03614853129546307</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1169573024803906</v>
+        <v>3.766774982348437e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02401739807408707</v>
+        <v>1.234450203673358e-14</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06458160944474904</v>
+        <v>1.162055568210802e-15</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02318420105852103</v>
+        <v>-9.274358141328043e-15</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4342309564434675</v>
+        <v>2.975709280618e-14</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1768107548196307</v>
+        <v>0.08511830162592438</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.192375271913432</v>
+        <v>6.571932954201019e-15</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05134642111001559</v>
+        <v>3.832535906606724e-14</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1091510868621818</v>
+        <v>0.06631465152517123</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0113638242336436</v>
+        <v>-1.095175438219599e-15</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.09942756446043967</v>
+        <v>1.196427894251039e-14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.06202759438232119</v>
+        <v>3.897475924526549e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01779449026639651</v>
+        <v>-3.937870466132445e-15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1900178179022771</v>
+        <v>-5.897148832472194e-15</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0302587164462409</v>
+        <v>-1.526286676003655e-15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7881480009900855</v>
+        <v>1.135528060123841</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08923865655749723</v>
+        <v>-7.1838072181542e-15</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.008925953845315013</v>
+        <v>-1.041520183079349e-15</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3754431112572981</v>
+        <v>-0.2018195271737721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06530206213172539</v>
+        <v>1.899886275937131e-15</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2032988944392223</v>
+        <v>-4.375839447173095e-16</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03612492124922895</v>
+        <v>-7.89019413088756e-15</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04177505169849061</v>
+        <v>3.903924729097887e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04479024300057588</v>
+        <v>-3.965737661690607e-15</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02404221597700784</v>
+        <v>-0.005859552357680204</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3861249367622085</v>
+        <v>-3.929730640637687e-15</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1093678467764281</v>
+        <v>1.430138833946997e-15</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3190136425720426</v>
+        <v>-0.03614853129546603</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2180000741486793</v>
+        <v>-1.364809959464882e-14</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1594280066529672</v>
+        <v>-8.195297217683246e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0734126125026561</v>
+        <v>1.472273984623347e-15</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001394895487279877</v>
+        <v>-2.342126582882045e-14</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07852848811720352</v>
+        <v>6.665861860010139e-15</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1967806166388088</v>
+        <v>0.08511830162593602</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02310555929975977</v>
+        <v>-1.655608316428279e-14</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.07271586853196223</v>
+        <v>-1.023076179346179e-15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2633552595574092</v>
+        <v>0.06631465152516935</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2335355740768847</v>
+        <v>-1.90878528910392e-14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1631798271935227</v>
+        <v>0.008573524431539383</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2135095479996891</v>
+        <v>-0.02956718859924126</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6980412247350894</v>
+        <v>-0.1890775731357466</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1189345233099394</v>
+        <v>2.153943972066077e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08923865655749723</v>
+        <v>-7.1838072181542e-15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4892520587542063</v>
+        <v>0.8414908275896859</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2231988442808829</v>
+        <v>-4.337711913302334e-15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2898073826258312</v>
+        <v>6.023055274222734e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1228263907023402</v>
+        <v>-0.2445028283693234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02094047074920728</v>
+        <v>0.003875030025990575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3303390443072198</v>
+        <v>-0.003585501122988979</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.093046347377671</v>
+        <v>0.05221776215030532</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001101561639857658</v>
+        <v>-1.37814934508565e-14</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1339805503161518</v>
+        <v>2.733550132719048e-16</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004031459586311908</v>
+        <v>-0.1655393321390331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05865433055893136</v>
+        <v>1.193779852062806e-15</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.05853046788540306</v>
+        <v>-2.947218180178534e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4035365251313385</v>
+        <v>-0.005742182997563516</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.01226051447158838</v>
+        <v>-0.03086206730206809</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0994118605949097</v>
+        <v>0.2128008577482631</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2825919729404073</v>
+        <v>0.07175412932632125</v>
       </c>
       <c r="V6" t="n">
-        <v>0.187563118768441</v>
+        <v>3.84924686424282e-15</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1146760223922846</v>
+        <v>-4.172274162846321e-15</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6833550986828032</v>
+        <v>-0.3200825066660519</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.2580481936865507</v>
+        <v>9.581925222400193e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.2650792734715772</v>
+        <v>1.342240724807009e-15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.430996556475864</v>
+        <v>-0.04112579733976429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.01700340897766904</v>
+        <v>-1.544464937652877e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.305343134968752</v>
+        <v>-1.137962990505073e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.213134475810546</v>
+        <v>-1.234117927627621e-17</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1100849562828111</v>
+        <v>-0.2018195271737731</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008925953845315013</v>
+        <v>-1.041520183079349e-15</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2231988442808829</v>
+        <v>-4.337711913302334e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8145067047835353</v>
+        <v>0.03708781228681771</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06813149350885016</v>
+        <v>1.075402466725284e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1923802406309588</v>
+        <v>1.346996006755339e-15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.198023267921867</v>
+        <v>1.19250595804578e-15</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2622710345588445</v>
+        <v>-4.113289086181815e-15</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06791619136208632</v>
+        <v>5.677914293175194e-15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05350579253795901</v>
+        <v>-0.03614853129546402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1796888656138701</v>
+        <v>-8.841477884205918e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02594724123843849</v>
+        <v>-4.007503648499687e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06169096675362779</v>
+        <v>0.01304087277637587</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1462297076904718</v>
+        <v>9.585055663512385e-17</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2467302932479496</v>
+        <v>-1.185965562008172e-15</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08228812368415675</v>
+        <v>5.635569625452977e-17</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2489558466252404</v>
+        <v>1.450914300037016e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2449098270213165</v>
+        <v>-4.484786025713352e-15</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2843329317940593</v>
+        <v>-0.01793042546452277</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3509960446419399</v>
+        <v>-1.579800017215935e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09231187255669455</v>
+        <v>-4.468018194407829e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.4539615560160546</v>
+        <v>-0.01396938018809992</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1583857783714741</v>
+        <v>1.382754645685104e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1862531593421351</v>
+        <v>-1.770911987742219e-15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.01310934176527894</v>
+        <v>-2.464799458951021e-16</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.1527188379035007</v>
+        <v>1.70356258769867e-15</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2629337532790755</v>
+        <v>6.997825498185122e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04510959276708901</v>
+        <v>5.672469226565263e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3754431112572981</v>
+        <v>-0.2018195271737721</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2898073826258312</v>
+        <v>6.023055274222734e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06813149350885016</v>
+        <v>1.075402466725284e-16</v>
       </c>
       <c r="H8" t="n">
-        <v>0.883768273296835</v>
+        <v>0.03708781228681745</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005188910809834281</v>
+        <v>-2.270325446870188e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06922734766925581</v>
+        <v>1.585905679090568e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4341439499924007</v>
+        <v>-3.481601629642925e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.693597212452047</v>
+        <v>-6.26818707852511e-15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09668201033637445</v>
+        <v>2.451609432759955e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1894559163729622</v>
+        <v>-0.03614853129546246</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2311663032610433</v>
+        <v>1.002831535248746e-15</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5137515770166476</v>
+        <v>-5.742084012616386e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4715373731893848</v>
+        <v>0.01304087277637619</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8067126932702743</v>
+        <v>2.234487413041541e-15</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01443036262215329</v>
+        <v>4.109058889317476e-16</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1332282539393445</v>
+        <v>-3.824479241714403e-16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.113291894304868</v>
+        <v>3.946373384794854e-15</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.006324366015951067</v>
+        <v>-1.012660187980458e-15</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.287431548593561</v>
+        <v>-0.01793042546452508</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4678768763184841</v>
+        <v>3.334276952595217e-15</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2025692145682991</v>
+        <v>2.865434351689654e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.6161268105428493</v>
+        <v>-0.01396938018809933</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7500216061177544</v>
+        <v>2.880346419820308e-15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1161740999958441</v>
+        <v>0.01969563737657378</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.200996398396036</v>
+        <v>-0.07078715831251735</v>
       </c>
       <c r="C9" t="n">
-        <v>4.495024505970179</v>
+        <v>0.08486288721808025</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07905262123336666</v>
+        <v>-5.575630527048868e-15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06530206213172539</v>
+        <v>1.899886275937131e-15</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1228263907023402</v>
+        <v>-0.2445028283693234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1923802406309588</v>
+        <v>1.346996006755339e-15</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005188910809834281</v>
+        <v>-2.270325446870188e-16</v>
       </c>
       <c r="I9" t="n">
-        <v>2.439916960148519</v>
+        <v>0.07930054706755627</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02383477369958672</v>
+        <v>-0.003492041624119291</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3084184137227971</v>
+        <v>0.007015030267732136</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5442021164954206</v>
+        <v>-0.03702968471917125</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03042968424291701</v>
+        <v>-7.48447095367167e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.589001127725274</v>
+        <v>5.343705644655884e-16</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3973345076319936</v>
+        <v>-0.005742182997556665</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4372600787679409</v>
+        <v>5.646526286045419e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5156366273615871</v>
+        <v>-7.891258214920766e-17</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.9008302458420673</v>
+        <v>0.01866858607642364</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1328811944121697</v>
+        <v>0.01108030847239892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6949666056553312</v>
+        <v>-0.05467504803415042</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.396133337827183</v>
+        <v>-0.0227505153267709</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1661521854618453</v>
+        <v>-2.023734285602028e-15</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3920337213007405</v>
+        <v>1.581314663203299e-15</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.003229772842886457</v>
+        <v>0.1152388551151542</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.5485014699652331</v>
+        <v>-5.569330130981129e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.09807114072336368</v>
+        <v>-3.255690089012758e-16</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.362696436116531</v>
+        <v>0.02894528888168646</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.2078067931183774</v>
+        <v>-4.41560759342019e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3134260700816869</v>
+        <v>0.009909728117547019</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3396723767934992</v>
+        <v>-0.03331951698959924</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03622607011510384</v>
+        <v>5.2262366862049e-16</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2032988944392223</v>
+        <v>-4.375839447173095e-16</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02094047074920728</v>
+        <v>0.003875030025990575</v>
       </c>
       <c r="G10" t="n">
-        <v>0.198023267921867</v>
+        <v>1.19250595804578e-15</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06922734766925581</v>
+        <v>1.585905679090568e-16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02383477369958672</v>
+        <v>-0.003492041624119291</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5800343179786569</v>
+        <v>1.056139924598387</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3001443872814949</v>
+        <v>-0.2880302128933753</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2271697095786892</v>
+        <v>0.1071925414148773</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004505331241764177</v>
+        <v>-1.595930940510158e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0308331080126089</v>
+        <v>-2.440069636324946e-16</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.005134402112020034</v>
+        <v>-0.008573524431538377</v>
       </c>
       <c r="P10" t="n">
-        <v>0.200191255723604</v>
+        <v>1.464019952434637e-16</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2696199112050799</v>
+        <v>2.243875192823305e-16</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0799594743572099</v>
+        <v>-0.01969563737657552</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.01811781296357244</v>
+        <v>0.00232223402115115</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02686723942114967</v>
+        <v>-0.0130627590912015</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.008957070802960833</v>
+        <v>-0.02856029426918377</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1550950463514231</v>
+        <v>-3.241730992635344e-15</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05921162370072334</v>
+        <v>2.032957821257694e-15</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07797446537288365</v>
+        <v>0.009214931426537629</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.08674663233922157</v>
+        <v>4.02644254527113e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.04826634951007563</v>
+        <v>-1.151169736925382e-15</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.3865370773588435</v>
+        <v>-0.05859469609200826</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1745743292832573</v>
+        <v>0.009909728117548075</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2444302676276843</v>
+        <v>-0.08140288302674654</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3634671591147606</v>
+        <v>0.1280626426563304</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05082543940799338</v>
+        <v>5.450773356742642e-15</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03612492124922895</v>
+        <v>-7.89019413088756e-15</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3303390443072198</v>
+        <v>-0.003585501122988979</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2622710345588445</v>
+        <v>-4.113289086181815e-15</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4341439499924007</v>
+        <v>-3.481601629642925e-16</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3084184137227971</v>
+        <v>0.007015030267732136</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3001443872814949</v>
+        <v>-0.2880302128933753</v>
       </c>
       <c r="K11" t="n">
-        <v>3.026417895045136</v>
+        <v>1.367857915220497</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.161046659498492</v>
+        <v>-0.3983966623683241</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2976026532290492</v>
+        <v>-1.253260790921188e-14</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0525717351183561</v>
+        <v>2.668634873301547e-15</v>
       </c>
       <c r="O11" t="n">
-        <v>0.008333135821483897</v>
+        <v>0.02956718859924099</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1026508071426947</v>
+        <v>1.920853935460631e-15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2183097849940894</v>
+        <v>-1.493151166404263e-15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66801410358781</v>
+        <v>0.0707871583125023</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2275457557440544</v>
+        <v>-0.01293754325852457</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3399747968693278</v>
+        <v>0.06677051010832616</v>
       </c>
       <c r="U11" t="n">
-        <v>1.879184743140948</v>
+        <v>0.1006846726786823</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0006994108747199472</v>
+        <v>1.386675892376127e-14</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1034885402931061</v>
+        <v>-9.706737420475487e-15</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3656143003076471</v>
+        <v>-0.06678716967014516</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2909907691243628</v>
+        <v>-2.980140847183516e-15</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.5818831297863566</v>
+        <v>5.311733332757056e-15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.270108191729374</v>
+        <v>0.2242719444264581</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1263089958957333</v>
+        <v>-0.03331951698960246</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.311735988600461</v>
+        <v>0.1280626426563356</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.184670637115342</v>
+        <v>-0.1038550674043969</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1786470417678356</v>
+        <v>-3.816248099857366e-14</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04177505169849061</v>
+        <v>3.903924729097887e-14</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.093046347377671</v>
+        <v>0.05221776215030532</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06791619136208632</v>
+        <v>5.677914293175194e-15</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.693597212452047</v>
+        <v>-6.26818707852511e-15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5442021164954206</v>
+        <v>-0.03702968471917125</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2271697095786892</v>
+        <v>0.1071925414148773</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.161046659498492</v>
+        <v>-0.3983966623683241</v>
       </c>
       <c r="L12" t="n">
-        <v>16.55118836287072</v>
+        <v>0.1814885846271134</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8057794940941736</v>
+        <v>5.103005733152018e-14</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.270237449228737</v>
+        <v>-4.055269553024726e-15</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6118990165435874</v>
+        <v>0.1890775731357324</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.510283879460019</v>
+        <v>-8.068042306054509e-15</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7773296387974552</v>
+        <v>-1.759157948931846e-16</v>
       </c>
       <c r="R12" t="n">
-        <v>-6.420500073198849</v>
+        <v>-0.08486288721807161</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.585450956427088</v>
+        <v>0.008556621213696972</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5119920761024324</v>
+        <v>-0.0447428551211576</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.43709798089367</v>
+        <v>-0.03188771358237799</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3805352963416703</v>
+        <v>3.101564665568179e-16</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3393735772481474</v>
+        <v>3.041206649899874e-15</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.41257740776895</v>
+        <v>-0.09424145154437441</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6350611172948484</v>
+        <v>1.315140414232715e-15</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.414736780282529</v>
+        <v>9.296453233549855e-16</v>
       </c>
       <c r="AA12" t="n">
-        <v>-10.31355311749109</v>
+        <v>-0.09862789552488897</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1285055644581466</v>
+        <v>3.386327417517696e-16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1665765601027066</v>
+        <v>-2.336738628937137e-15</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.8040308144744107</v>
+        <v>-1.604400350251715e-14</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2693792778506841</v>
+        <v>-0.005859552357678273</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04479024300057588</v>
+        <v>-3.965737661690607e-15</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.001101561639857658</v>
+        <v>-1.37814934508565e-14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05350579253795901</v>
+        <v>-0.03614853129546402</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.09668201033637445</v>
+        <v>2.451609432759955e-15</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03042968424291701</v>
+        <v>-7.48447095367167e-16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004505331241764177</v>
+        <v>-1.595930940510158e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2976026532290492</v>
+        <v>-1.253260790921188e-14</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8057794940941736</v>
+        <v>5.103005733152018e-14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7019426891329777</v>
+        <v>1.135528060123846</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0314978762790113</v>
+        <v>-2.156058555255871e-15</v>
       </c>
       <c r="O13" t="n">
-        <v>0.005175211335298458</v>
+        <v>-9.21239030247837e-15</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3079438307448016</v>
+        <v>-0.201819527173774</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.09228659644120316</v>
+        <v>1.878025513333593e-15</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2374333376988828</v>
+        <v>-1.759623152189115e-14</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2043690668761826</v>
+        <v>-1.583502000704091e-15</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.112857729859229</v>
+        <v>8.23802258874312e-15</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1446332869030397</v>
+        <v>-2.789481786957762e-14</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1141374982539353</v>
+        <v>0.08511830162591912</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1458866730568176</v>
+        <v>6.940567578104581e-15</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1003044053372842</v>
+        <v>-2.485074303061159e-14</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1395123102893328</v>
+        <v>0.06631465152517331</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1160899006672987</v>
+        <v>-2.628157884005778e-15</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.6387330212246657</v>
+        <v>-2.884382267566619e-14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1173043569348611</v>
+        <v>6.31796188350958e-17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.1036776627857329</v>
+        <v>-1.346720420001046e-15</v>
       </c>
       <c r="C14" t="n">
-        <v>1.065561755274843</v>
+        <v>2.584755919814277e-15</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06524060910164985</v>
+        <v>-2.067450063437449e-16</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02404221597700784</v>
+        <v>-0.005859552357680204</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1339805503161518</v>
+        <v>2.733550132719048e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1796888656138701</v>
+        <v>-8.841477884205918e-16</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1894559163729622</v>
+        <v>-0.03614853129546246</v>
       </c>
       <c r="I14" t="n">
-        <v>0.589001127725274</v>
+        <v>5.343705644655884e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0308331080126089</v>
+        <v>-2.440069636324946e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0525717351183561</v>
+        <v>2.668634873301547e-15</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.270237449228737</v>
+        <v>-4.055269553024726e-15</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0314978762790113</v>
+        <v>-2.156058555255871e-15</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4175012091078372</v>
+        <v>1.135528060123846</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1548229434925195</v>
+        <v>-1.439926491574113e-15</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1365606174312021</v>
+        <v>3.428734716821045e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1984352032131838</v>
+        <v>-0.2018195271737742</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.09370370032051814</v>
+        <v>1.879233234315659e-15</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07900881569095916</v>
+        <v>4.025962915387903e-16</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1304390533883987</v>
+        <v>-3.842492595752732e-15</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7176149626538778</v>
+        <v>3.048154181461469e-15</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01505980572682096</v>
+        <v>-7.727800923050603e-16</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01663849525384534</v>
+        <v>0.0851183016259294</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1716624283443019</v>
+        <v>-2.911988268780397e-15</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1913306413657045</v>
+        <v>3.30013690195977e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01074579781212876</v>
+        <v>0.06631465152516755</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6677729960237342</v>
+        <v>4.193736780505097e-15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.08134899582738155</v>
+        <v>-0.003875030025991172</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2356088425466359</v>
+        <v>0.003585501122984139</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2530626625369093</v>
+        <v>-0.0522177621502811</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03174796937395418</v>
+        <v>1.350674140835183e-14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3861249367622085</v>
+        <v>-3.929730640637687e-15</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.004031459586311908</v>
+        <v>-0.1655393321390331</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02594724123843849</v>
+        <v>-4.007503648499687e-15</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2311663032610433</v>
+        <v>1.002831535248746e-15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3973345076319936</v>
+        <v>-0.005742182997556665</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.005134402112020034</v>
+        <v>-0.008573524431538377</v>
       </c>
       <c r="K15" t="n">
-        <v>0.008333135821483897</v>
+        <v>0.02956718859924099</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6118990165435874</v>
+        <v>0.1890775731357324</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005175211335298458</v>
+        <v>-9.21239030247837e-15</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1548229434925195</v>
+        <v>-1.439926491574113e-15</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5758762885586406</v>
+        <v>0.8414908275896715</v>
       </c>
       <c r="P15" t="n">
-        <v>0.008131043216929234</v>
+        <v>5.45164442965007e-16</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1832176581845454</v>
+        <v>2.398712304801362e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.4493534416995106</v>
+        <v>-0.2445028283693172</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02017498608661599</v>
+        <v>0.03086206730207043</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2073050428927997</v>
+        <v>-0.2128008577482741</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2730910805135484</v>
+        <v>-0.07175412932632715</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1304673536498873</v>
+        <v>1.462992909097389e-14</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.006225635587144885</v>
+        <v>-9.327075507311437e-15</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1556899884293735</v>
+        <v>-0.3200825066660518</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1351492648193002</v>
+        <v>-1.4058061348023e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2715904030348914</v>
+        <v>2.00540657752214e-15</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6030027521051288</v>
+        <v>-0.04112579733974672</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.1205691247169175</v>
+        <v>1.444733700211302e-16</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.3157358118738263</v>
+        <v>-5.079632101687527e-16</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9182837456742124</v>
+        <v>3.187534276902286e-15</v>
       </c>
       <c r="D16" t="n">
-        <v>0.054352283599816</v>
+        <v>-0.03614853129546307</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1093678467764281</v>
+        <v>1.430138833946997e-15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05865433055893136</v>
+        <v>1.193779852062806e-15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06169096675362779</v>
+        <v>0.01304087277637587</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5137515770166476</v>
+        <v>-5.742084012616386e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4372600787679409</v>
+        <v>5.646526286045419e-16</v>
       </c>
       <c r="J16" t="n">
-        <v>0.200191255723604</v>
+        <v>1.464019952434637e-16</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1026508071426947</v>
+        <v>1.920853935460631e-15</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.510283879460019</v>
+        <v>-8.068042306054509e-15</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3079438307448016</v>
+        <v>-0.201819527173774</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1365606174312021</v>
+        <v>3.428734716821045e-16</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008131043216929234</v>
+        <v>5.45164442965007e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6755256862683895</v>
+        <v>0.03708781228681799</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1525359272821717</v>
+        <v>-3.612357089115043e-16</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2613756116250616</v>
+        <v>2.955552385848179e-15</v>
       </c>
       <c r="S16" t="n">
-        <v>0.10164338759066</v>
+        <v>2.5218366816907e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2200193440587406</v>
+        <v>-1.184490322053654e-15</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09587048814305606</v>
+        <v>3.933061125095855e-15</v>
       </c>
       <c r="V16" t="n">
-        <v>0.057452862176569</v>
+        <v>-0.017930425464522</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2588241122705794</v>
+        <v>-1.402404523909958e-15</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1210872517075963</v>
+        <v>3.715010748694875e-15</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.1236198547946901</v>
+        <v>-0.01396938018810022</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.3206522505589467</v>
+        <v>5.401632045206565e-16</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.7164263842460219</v>
+        <v>4.897438112283234e-15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1672446946576478</v>
+        <v>-3.160818440098758e-16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2313498355330804</v>
+        <v>1.68307476419551e-15</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.368226769666174</v>
+        <v>-6.091245149046563e-16</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1169573024803906</v>
+        <v>3.766774982348437e-16</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3190136425720426</v>
+        <v>-0.03614853129546603</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05853046788540306</v>
+        <v>-2.947218180178534e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1462297076904718</v>
+        <v>9.585055663512385e-17</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4715373731893848</v>
+        <v>0.01304087277637619</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5156366273615871</v>
+        <v>-7.891258214920766e-17</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2696199112050799</v>
+        <v>2.243875192823305e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2183097849940894</v>
+        <v>-1.493151166404263e-15</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7773296387974552</v>
+        <v>-1.759157948931846e-16</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09228659644120316</v>
+        <v>1.878025513333593e-15</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1984352032131838</v>
+        <v>-0.2018195271737742</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1832176581845454</v>
+        <v>2.398712304801362e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1525359272821717</v>
+        <v>-3.612357089115043e-16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8861202738067419</v>
+        <v>0.03708781228681827</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6280106986494407</v>
+        <v>1.117477615183003e-16</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.02051021861685338</v>
+        <v>2.14483827946945e-16</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.04548425048685018</v>
+        <v>5.565446093717616e-16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.734691453001671</v>
+        <v>2.064309032091808e-16</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1005661050670076</v>
+        <v>4.340170944487027e-17</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2643615340319093</v>
+        <v>-0.0179304254645245</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.02937622776570563</v>
+        <v>1.45379160704949e-15</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1800619705504645</v>
+        <v>7.16060191689248e-17</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.3967600083789445</v>
+        <v>-0.01396938018809935</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.2165110188458217</v>
+        <v>-4.822311281547051e-16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.003426113867490373</v>
+        <v>0.003492041624121089</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4813350308291595</v>
+        <v>-0.007015030267726976</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0696969552455096</v>
+        <v>0.03702968471916351</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.02401739807408707</v>
+        <v>1.234450203673358e-14</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2180000741486793</v>
+        <v>-1.364809959464882e-14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4035365251313385</v>
+        <v>-0.005742182997563516</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2467302932479496</v>
+        <v>-1.185965562008172e-15</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8067126932702743</v>
+        <v>2.234487413041541e-15</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9008302458420673</v>
+        <v>0.01866858607642364</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0799594743572099</v>
+        <v>-0.01969563737657552</v>
       </c>
       <c r="K18" t="n">
-        <v>1.66801410358781</v>
+        <v>0.0707871583125023</v>
       </c>
       <c r="L18" t="n">
-        <v>-6.420500073198849</v>
+        <v>-0.08486288721807161</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2374333376988828</v>
+        <v>-1.759623152189115e-14</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09370370032051814</v>
+        <v>1.879233234315659e-15</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4493534416995106</v>
+        <v>-0.2445028283693172</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2613756116250616</v>
+        <v>2.955552385848179e-15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6280106986494407</v>
+        <v>1.117477615183003e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.99384122905962</v>
+        <v>0.07930054706755287</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5501310855261069</v>
+        <v>-0.01108030847239677</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2650376181166659</v>
+        <v>0.05467504803415046</v>
       </c>
       <c r="U18" t="n">
-        <v>3.833014585399434</v>
+        <v>0.02275051532677107</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1317547815048816</v>
+        <v>-4.13618913604229e-15</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2653816183163183</v>
+        <v>1.531927186420996e-15</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4794268806940409</v>
+        <v>0.1152388551151562</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1687006959201578</v>
+        <v>1.170220191820075e-17</v>
       </c>
       <c r="Z18" t="n">
-        <v>-1.064868018657193</v>
+        <v>-1.181881993210751e-15</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.260581998687542</v>
+        <v>0.02894528888167856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.002887341203119973</v>
+        <v>0.002322234021151529</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01675257734977409</v>
+        <v>-0.01293754325852874</v>
       </c>
       <c r="C19" t="n">
-        <v>1.047427326759348</v>
+        <v>0.008556621213709887</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06458160944474904</v>
+        <v>1.162055568210802e-15</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1594280066529672</v>
+        <v>-8.195297217683246e-16</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01226051447158838</v>
+        <v>-0.03086206730206809</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.08228812368415675</v>
+        <v>5.635569625452977e-17</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01443036262215329</v>
+        <v>4.109058889317476e-16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1328811944121697</v>
+        <v>0.01108030847239892</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.01811781296357244</v>
+        <v>0.00232223402115115</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2275457557440544</v>
+        <v>-0.01293754325852457</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.585450956427088</v>
+        <v>0.008556621213696972</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2043690668761826</v>
+        <v>-1.583502000704091e-15</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07900881569095916</v>
+        <v>4.025962915387903e-16</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02017498608661599</v>
+        <v>0.03086206730207043</v>
       </c>
       <c r="P19" t="n">
-        <v>0.10164338759066</v>
+        <v>2.5218366816907e-16</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.02051021861685338</v>
+        <v>2.14483827946945e-16</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5501310855261069</v>
+        <v>-0.01108030847239677</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3297369179302865</v>
+        <v>1.011727530350755</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05910329156124965</v>
+        <v>-0.05206058578541711</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2476484747251921</v>
+        <v>0.003919016483747578</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0356590455028916</v>
+        <v>2.966680154983287e-16</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.01599436614132976</v>
+        <v>-5.201986291875185e-17</v>
       </c>
       <c r="X19" t="n">
-        <v>0.02470037462206829</v>
+        <v>-6.019591554988281e-16</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.02487361775223059</v>
+        <v>-1.7994999724766e-16</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.1427147297812503</v>
+        <v>-3.747537437217278e-16</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.499148303130219</v>
+        <v>8.130298161367387e-15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1051860925764446</v>
+        <v>-0.01306275909120277</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3483231732877</v>
+        <v>0.06677051010835432</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6431942298007601</v>
+        <v>-0.04474285512117276</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02318420105852103</v>
+        <v>-9.274358141328043e-15</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0734126125026561</v>
+        <v>1.472273984623347e-15</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0994118605949097</v>
+        <v>0.2128008577482631</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2489558466252404</v>
+        <v>1.450914300037016e-15</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1332282539393445</v>
+        <v>-3.824479241714403e-16</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6949666056553312</v>
+        <v>-0.05467504803415042</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02686723942114967</v>
+        <v>-0.0130627590912015</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3399747968693278</v>
+        <v>0.06677051010832616</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5119920761024324</v>
+        <v>-0.0447428551211576</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.112857729859229</v>
+        <v>8.23802258874312e-15</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1304390533883987</v>
+        <v>-3.842492595752732e-15</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2073050428927997</v>
+        <v>-0.2128008577482741</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2200193440587406</v>
+        <v>-1.184490322053654e-15</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.04548425048685018</v>
+        <v>5.565446093717616e-16</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2650376181166659</v>
+        <v>0.05467504803415046</v>
       </c>
       <c r="S20" t="n">
-        <v>0.05910329156124965</v>
+        <v>-0.05206058578541711</v>
       </c>
       <c r="T20" t="n">
-        <v>0.424351537254969</v>
+        <v>0.09979204085798048</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4314891604587402</v>
+        <v>0.04176012516550072</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.05619984045743012</v>
+        <v>-1.978260434089456e-15</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1124560617581116</v>
+        <v>6.976350152503874e-16</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.11467840225868</v>
+        <v>6.991411850742648e-15</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.3067773636643468</v>
+        <v>3.909807990392275e-16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1147401990000802</v>
+        <v>-1.325032232692428e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.1672338619348848</v>
+        <v>-8.329386249341701e-15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.1108421246107498</v>
+        <v>-0.02856029426917964</v>
       </c>
       <c r="B21" t="n">
-        <v>2.191099469329304</v>
+        <v>0.1006846726786921</v>
       </c>
       <c r="C21" t="n">
-        <v>-6.965370068784794</v>
+        <v>-0.03188771358238395</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4342309564434675</v>
+        <v>2.975709280618e-14</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001394895487279877</v>
+        <v>-2.342126582882045e-14</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2825919729404073</v>
+        <v>0.07175412932632125</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2449098270213165</v>
+        <v>-4.484786025713352e-15</v>
       </c>
       <c r="H21" t="n">
-        <v>1.113291894304868</v>
+        <v>3.946373384794854e-15</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.396133337827183</v>
+        <v>-0.0227505153267709</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.008957070802960833</v>
+        <v>-0.02856029426918377</v>
       </c>
       <c r="K21" t="n">
-        <v>1.879184743140948</v>
+        <v>0.1006846726786823</v>
       </c>
       <c r="L21" t="n">
-        <v>-6.43709798089367</v>
+        <v>-0.03188771358237799</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1446332869030397</v>
+        <v>-2.789481786957762e-14</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7176149626538778</v>
+        <v>3.048154181461469e-15</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2730910805135484</v>
+        <v>-0.07175412932632715</v>
       </c>
       <c r="P21" t="n">
-        <v>0.09587048814305606</v>
+        <v>3.933061125095855e-15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.734691453001671</v>
+        <v>2.064309032091808e-16</v>
       </c>
       <c r="R21" t="n">
-        <v>3.833014585399434</v>
+        <v>0.02275051532677107</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2476484747251921</v>
+        <v>0.003919016483747578</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4314891604587402</v>
+        <v>0.04176012516550072</v>
       </c>
       <c r="U21" t="n">
-        <v>9.171245456828867</v>
+        <v>0.02696172541220905</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3421105256192215</v>
+        <v>-3.322529622859444e-17</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4547890701018952</v>
+        <v>-1.487509390266503e-15</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8184425049446132</v>
+        <v>2.774270032574293e-15</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2435017530872471</v>
+        <v>2.524317453596344e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>-1.070811162606688</v>
+        <v>-1.080578631220892e-15</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.8111470211552311</v>
+        <v>-3.628646234064983e-15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.07460627977017599</v>
+        <v>9.867811080087707e-16</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.6003953609481625</v>
+        <v>-5.944950718855072e-15</v>
       </c>
       <c r="C22" t="n">
-        <v>1.26120655825385</v>
+        <v>-5.481556824273983e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1768107548196307</v>
+        <v>0.08511830162592438</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07852848811720352</v>
+        <v>6.665861860010139e-15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.187563118768441</v>
+        <v>3.84924686424282e-15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2843329317940593</v>
+        <v>-0.01793042546452277</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.006324366015951067</v>
+        <v>-1.012660187980458e-15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1661521854618453</v>
+        <v>-2.023734285602028e-15</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1550950463514231</v>
+        <v>-3.241730992635344e-15</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0006994108747199472</v>
+        <v>1.386675892376127e-14</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3805352963416703</v>
+        <v>3.101564665568179e-16</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1141374982539353</v>
+        <v>0.08511830162591912</v>
       </c>
       <c r="N22" t="n">
-        <v>0.01505980572682096</v>
+        <v>-7.727800923050603e-16</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1304673536498873</v>
+        <v>1.462992909097389e-14</v>
       </c>
       <c r="P22" t="n">
-        <v>0.057452862176569</v>
+        <v>-0.017930425464522</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1005661050670076</v>
+        <v>4.340170944487027e-17</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1317547815048816</v>
+        <v>-4.13618913604229e-15</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0356590455028916</v>
+        <v>2.966680154983287e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.05619984045743012</v>
+        <v>-1.978260434089456e-15</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3421105256192215</v>
+        <v>-3.322529622859444e-17</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3840937896995534</v>
+        <v>0.01282699344431238</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1688349116125346</v>
+        <v>1.50733253086064e-15</v>
       </c>
       <c r="X22" t="n">
-        <v>0.07756797984861555</v>
+        <v>-8.063854079908012e-15</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.1950765389853803</v>
+        <v>0.009993357293635183</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.1440281167481682</v>
+        <v>1.008715436472186e-16</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.8210467046785628</v>
+        <v>8.040602155828484e-16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.001208669037817883</v>
+        <v>-8.177888879738922e-16</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1132844784114047</v>
+        <v>4.6633436322233e-15</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.4647946639524154</v>
+        <v>-4.942166928248169e-16</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.192375271913432</v>
+        <v>6.571932954201019e-15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1967806166388088</v>
+        <v>0.08511830162593602</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1146760223922846</v>
+        <v>-4.172274162846321e-15</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3509960446419399</v>
+        <v>-1.579800017215935e-15</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.287431548593561</v>
+        <v>-0.01793042546452508</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3920337213007405</v>
+        <v>1.581314663203299e-15</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05921162370072334</v>
+        <v>2.032957821257694e-15</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1034885402931061</v>
+        <v>-9.706737420475487e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3393735772481474</v>
+        <v>3.041206649899874e-15</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1458866730568176</v>
+        <v>6.940567578104581e-15</v>
       </c>
       <c r="N23" t="n">
-        <v>0.01663849525384534</v>
+        <v>0.0851183016259294</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.006225635587144885</v>
+        <v>-9.327075507311437e-15</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2588241122705794</v>
+        <v>-1.402404523909958e-15</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2643615340319093</v>
+        <v>-0.0179304254645245</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2653816183163183</v>
+        <v>1.531927186420996e-15</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01599436614132976</v>
+        <v>-5.201986291875185e-17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1124560617581116</v>
+        <v>6.976350152503874e-16</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4547890701018952</v>
+        <v>-1.487509390266503e-15</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1688349116125346</v>
+        <v>1.50733253086064e-15</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4491191855011086</v>
+        <v>0.01282699344431573</v>
       </c>
       <c r="X23" t="n">
-        <v>0.03276013788615207</v>
+        <v>5.009936386306954e-15</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.0544640663261712</v>
+        <v>7.76015901657378e-16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.09914213280674491</v>
+        <v>0.009993357293635935</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.1413098208071</v>
+        <v>-2.523474776599761e-15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.2055228808198214</v>
+        <v>-0.009214931426535856</v>
       </c>
       <c r="B24" t="n">
-        <v>0.03603792382736411</v>
+        <v>0.06678716967013644</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3269147352865343</v>
+        <v>0.09424145154437029</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05134642111001559</v>
+        <v>3.832535906606724e-14</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.02310555929975977</v>
+        <v>-1.655608316428279e-14</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6833550986828032</v>
+        <v>-0.3200825066660519</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09231187255669455</v>
+        <v>-4.468018194407829e-15</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4678768763184841</v>
+        <v>3.334276952595217e-15</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.003229772842886457</v>
+        <v>0.1152388551151542</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07797446537288365</v>
+        <v>0.009214931426537629</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3656143003076471</v>
+        <v>-0.06678716967014516</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.41257740776895</v>
+        <v>-0.09424145154437441</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1003044053372842</v>
+        <v>-2.485074303061159e-14</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1716624283443019</v>
+        <v>-2.911988268780397e-15</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1556899884293735</v>
+        <v>-0.3200825066660518</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1210872517075963</v>
+        <v>3.715010748694875e-15</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.02937622776570563</v>
+        <v>1.45379160704949e-15</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4794268806940409</v>
+        <v>0.1152388551151562</v>
       </c>
       <c r="S24" t="n">
-        <v>0.02470037462206829</v>
+        <v>-6.019591554988281e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.11467840225868</v>
+        <v>6.991411850742648e-15</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8184425049446132</v>
+        <v>2.774270032574293e-15</v>
       </c>
       <c r="V24" t="n">
-        <v>0.07756797984861555</v>
+        <v>-8.063854079908012e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>0.03276013788615207</v>
+        <v>5.009936386306954e-15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.218052932663442</v>
+        <v>0.3072716531773037</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.2991364101817737</v>
+        <v>1.52176199363659e-15</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.2819447761465337</v>
+        <v>-3.410396609494134e-15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.009825138686816679</v>
+        <v>0.02206056604690382</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.1005123871607017</v>
+        <v>-5.19644120032156e-16</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5773482100575251</v>
+        <v>2.740115225207197e-15</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.431276599340738</v>
+        <v>-1.665275719496698e-15</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1091510868621818</v>
+        <v>0.06631465152517123</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07271586853196223</v>
+        <v>-1.023076179346179e-15</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2580481936865507</v>
+        <v>9.581925222400193e-16</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4539615560160546</v>
+        <v>-0.01396938018809992</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2025692145682991</v>
+        <v>2.865434351689654e-16</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5485014699652331</v>
+        <v>-5.569330130981129e-16</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.08674663233922157</v>
+        <v>4.02644254527113e-16</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2909907691243628</v>
+        <v>-2.980140847183516e-15</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6350611172948484</v>
+        <v>1.315140414232715e-15</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1395123102893328</v>
+        <v>0.06631465152517331</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1913306413657045</v>
+        <v>3.30013690195977e-16</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1351492648193002</v>
+        <v>-1.4058061348023e-15</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1236198547946901</v>
+        <v>-0.01396938018810022</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1800619705504645</v>
+        <v>7.16060191689248e-17</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1687006959201578</v>
+        <v>1.170220191820075e-17</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.02487361775223059</v>
+        <v>-1.7994999724766e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3067773636643468</v>
+        <v>3.909807990392275e-16</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2435017530872471</v>
+        <v>2.524317453596344e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1950765389853803</v>
+        <v>0.009993357293635183</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.0544640663261712</v>
+        <v>7.76015901657378e-16</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2991364101817737</v>
+        <v>1.52176199363659e-15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.8124186167008874</v>
+        <v>0.007785705234185932</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.305331681616373</v>
+        <v>-2.321324549470079e-16</v>
       </c>
       <c r="AA25" t="n">
-        <v>-1.196996802932891</v>
+        <v>-1.679057777418209e-15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.02988812232989752</v>
+        <v>7.76283353904702e-16</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2840147940456794</v>
+        <v>-3.909294601961608e-15</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8984252603624675</v>
+        <v>5.799998432542377e-16</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0113638242336436</v>
+        <v>-1.095175438219599e-15</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2633552595574092</v>
+        <v>0.06631465152516935</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2650792734715772</v>
+        <v>1.342240724807009e-15</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1583857783714741</v>
+        <v>1.382754645685104e-16</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6161268105428493</v>
+        <v>-0.01396938018809933</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09807114072336368</v>
+        <v>-3.255690089012758e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04826634951007563</v>
+        <v>-1.151169736925382e-15</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5818831297863566</v>
+        <v>5.311733332757056e-15</v>
       </c>
       <c r="L26" t="n">
-        <v>2.414736780282529</v>
+        <v>9.296453233549855e-16</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1160899006672987</v>
+        <v>-2.628157884005778e-15</v>
       </c>
       <c r="N26" t="n">
-        <v>0.01074579781212876</v>
+        <v>0.06631465152516755</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2715904030348914</v>
+        <v>2.00540657752214e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3206522505589467</v>
+        <v>5.401632045206565e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.3967600083789445</v>
+        <v>-0.01396938018809935</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.064868018657193</v>
+        <v>-1.181881993210751e-15</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1427147297812503</v>
+        <v>-3.747537437217278e-16</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1147401990000802</v>
+        <v>-1.325032232692428e-16</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.070811162606688</v>
+        <v>-1.080578631220892e-15</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1440281167481682</v>
+        <v>1.008715436472186e-16</v>
       </c>
       <c r="W26" t="n">
-        <v>0.09914213280674491</v>
+        <v>0.009993357293635935</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2819447761465337</v>
+        <v>-3.410396609494134e-15</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.305331681616373</v>
+        <v>-2.321324549470079e-16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6509294778463737</v>
+        <v>0.007785705234185067</v>
       </c>
       <c r="AA26" t="n">
-        <v>-1.694348415177251</v>
+        <v>2.907912428709058e-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.04285544467147286</v>
+        <v>0.05859469609200812</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.915484044500383</v>
+        <v>-0.2242719444264757</v>
       </c>
       <c r="C27" t="n">
-        <v>10.05836529264401</v>
+        <v>0.09862789552489724</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09942756446043967</v>
+        <v>1.196427894251039e-14</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2335355740768847</v>
+        <v>-1.90878528910392e-14</v>
       </c>
       <c r="F27" t="n">
-        <v>0.430996556475864</v>
+        <v>-0.04112579733976429</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1862531593421351</v>
+        <v>-1.770911987742219e-15</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7500216061177544</v>
+        <v>2.880346419820308e-15</v>
       </c>
       <c r="I27" t="n">
-        <v>2.362696436116531</v>
+        <v>0.02894528888168646</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3865370773588435</v>
+        <v>-0.05859469609200826</v>
       </c>
       <c r="K27" t="n">
-        <v>2.270108191729374</v>
+        <v>0.2242719444264581</v>
       </c>
       <c r="L27" t="n">
-        <v>-10.31355311749109</v>
+        <v>-0.09862789552488897</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6387330212246657</v>
+        <v>-2.884382267566619e-14</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6677729960237342</v>
+        <v>4.193736780505097e-15</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.6030027521051288</v>
+        <v>-0.04112579733974672</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7164263842460219</v>
+        <v>4.897438112283234e-15</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.2165110188458217</v>
+        <v>-4.822311281547051e-16</v>
       </c>
       <c r="R27" t="n">
-        <v>3.260581998687542</v>
+        <v>0.02894528888167856</v>
       </c>
       <c r="S27" t="n">
-        <v>1.499148303130219</v>
+        <v>8.130298161367387e-15</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1672338619348848</v>
+        <v>-8.329386249341701e-15</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8111470211552311</v>
+        <v>-3.628646234064983e-15</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8210467046785628</v>
+        <v>8.040602155828484e-16</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.1413098208071</v>
+        <v>-2.523474776599761e-15</v>
       </c>
       <c r="X27" t="n">
-        <v>0.009825138686816679</v>
+        <v>0.02206056604690382</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.196996802932891</v>
+        <v>-1.679057777418209e-15</v>
       </c>
       <c r="Z27" t="n">
-        <v>-1.694348415177251</v>
+        <v>2.907912428709058e-16</v>
       </c>
       <c r="AA27" t="n">
-        <v>11.60265930382697</v>
+        <v>0.07575795092305984</v>
       </c>
     </row>
   </sheetData>
